--- a/survey_templates/022_employee_attitude_survey--survey_templates.xlsx
+++ b/survey_templates/022_employee_attitude_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,46 +515,54 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_survey</t>
+          <t>employee_satisfaction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>How do you feel about your work environment?</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Overall, how would you rate your job satisfaction?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Choose the best answer for you.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_security</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How satisfied are you with your job?</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How satisfied are you with your job security?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Select one of the options</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +574,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>work_life_balance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>How do you feel about communication among team members?</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>How would you rate your work-life balance?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Choose the best answer for you.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>manager_support</t>
+          <t>stress_level</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>How much support do you receive from your manager?</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you feel stressed about work?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose the best answer for you.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,133 +628,157 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>manager_support</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>How do you feel about your work-life balance?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How would you rate your manager's support?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select one of the options</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>employee_satisfaction</t>
+          <t>hours_worked</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How satisfied are you with your job?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How many hours do you typically work per week?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter a number</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>working_hours</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Any feedback about your work environment?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>What are your working hours?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Choose the best answer for you.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>employee_survey_8</t>
+          <t>autonomy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How do you feel about your work environment?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How much autonomy do you have in your work?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select one of the options</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>job_satisfaction_9</t>
+          <t>feedback_manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>How satisfied are you with your job?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>How would you rate the level of feedback you receive from your manager?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select one of the options</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>communication_10</t>
+          <t>clear_goals</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>How do you feel about communication among team members?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Do you feel like your goals and expectations are clear?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Choose the best answer for you.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>manager_support_11</t>
+          <t>collaboration</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>How much support do you receive from your manager?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How would you rate your collaboration with colleagues?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Choose the best answer for you.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Any other comments or suggestions about your work environment?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Enter your thoughts</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -776,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -804,41 +875,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>employee_survey_choices</t>
+          <t>employee_satisfaction_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>employee_survey_choices</t>
+          <t>employee_satisfaction_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>employee_survey_choices</t>
+          <t>employee_satisfaction_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -855,476 +926,561 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>employee_survey_choices</t>
+          <t>employee_satisfaction_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>employee_survey_choices</t>
+          <t>employee_satisfaction_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Very Bad</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_security_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>highly_satisfied</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Highly Satisfied</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_security_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_security_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_security_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>work_life_balance_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>communication_choices</t>
+          <t>stress_level_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Very Bad</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>stress_level_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>stress_level_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>manager_support_choices</t>
+          <t>stress_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Very Good</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>manager_support_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bad</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>autonomy_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>very_bad</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Very Bad</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>employee_satisfaction_choices</t>
+          <t>autonomy_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>highly_satisfied</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Highly Satisfied</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>employee_satisfaction_choices</t>
+          <t>autonomy_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>employee_satisfaction_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>employee_satisfaction_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>employee_satisfaction_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>manager_support_11_choices</t>
+          <t>feedback_manager_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>manager_support_11_choices</t>
+          <t>clear_goals_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>manager_support_11_choices</t>
+          <t>clear_goals_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>very_good</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Very Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>bad</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Bad</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>collaboration_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>very_bad</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
